--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67944091</v>
+        <v>67943914</v>
       </c>
       <c r="B2" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689904.0428216576</v>
+        <v>689903</v>
       </c>
       <c r="R2" t="n">
-        <v>6371548.987167462</v>
+        <v>6371486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +745,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,15 +775,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67944366</v>
+        <v>67944271</v>
       </c>
       <c r="B3" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +786,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689904.1929345736</v>
+        <v>689912</v>
       </c>
       <c r="R3" t="n">
-        <v>6371615.281147022</v>
+        <v>6371587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,37 +875,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67943929</v>
+        <v>67946707</v>
       </c>
       <c r="B4" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689918.0395561449</v>
+        <v>689899</v>
       </c>
       <c r="R4" t="n">
-        <v>6371491.974350056</v>
+        <v>6371639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67944426</v>
+        <v>67947070</v>
       </c>
       <c r="B5" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689917.2367253811</v>
+        <v>689835</v>
       </c>
       <c r="R5" t="n">
-        <v>6371625.0506297</v>
+        <v>6371544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,19 +1045,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,37 +1075,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67944007</v>
+        <v>67947086</v>
       </c>
       <c r="B6" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>473</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689886.8762025242</v>
+        <v>689822</v>
       </c>
       <c r="R6" t="n">
-        <v>6371500.222738158</v>
+        <v>6371611</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,19 +1145,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,37 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67944120</v>
+        <v>67947110</v>
       </c>
       <c r="B7" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>689938.851881308</v>
+        <v>689880</v>
       </c>
       <c r="R7" t="n">
-        <v>6371566.777278381</v>
+        <v>6371604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,19 +1245,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,37 +1275,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67944455</v>
+        <v>67947116</v>
       </c>
       <c r="B8" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689927.1856759624</v>
+        <v>689876</v>
       </c>
       <c r="R8" t="n">
-        <v>6371620.125227399</v>
+        <v>6371613</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,19 +1345,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,15 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67947116</v>
+        <v>67947164</v>
       </c>
       <c r="B9" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689876.2256883241</v>
+        <v>689799</v>
       </c>
       <c r="R9" t="n">
-        <v>6371612.899953701</v>
+        <v>6371632</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,19 +1445,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,37 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67943938</v>
+        <v>67947180</v>
       </c>
       <c r="B10" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>689918.0395561449</v>
+        <v>689771</v>
       </c>
       <c r="R10" t="n">
-        <v>6371491.974350056</v>
+        <v>6371714</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,19 +1545,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,37 +1575,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67943995</v>
+        <v>67947185</v>
       </c>
       <c r="B11" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1752,10 +1612,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>689893.9559227705</v>
+        <v>689788</v>
       </c>
       <c r="R11" t="n">
-        <v>6371498.935876019</v>
+        <v>6371728</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,19 +1645,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,15 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67944041</v>
+        <v>67947225</v>
       </c>
       <c r="B12" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>689875.0975444769</v>
+        <v>689692</v>
       </c>
       <c r="R12" t="n">
-        <v>6371498.057075401</v>
+        <v>6371761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,19 +1745,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,39 +1775,30 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>67947062</v>
+        <v>67947158</v>
       </c>
       <c r="B13" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1982,10 +1808,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>689861.8408516926</v>
+        <v>689793</v>
       </c>
       <c r="R13" t="n">
-        <v>6371573.966576695</v>
+        <v>6371631</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,19 +1841,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,15 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>67943914</v>
+        <v>67944055</v>
       </c>
       <c r="B14" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2071,21 +1882,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2097,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>689903.2034473564</v>
+        <v>689869</v>
       </c>
       <c r="R14" t="n">
-        <v>6371485.893585891</v>
+        <v>6371495</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,19 +1941,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,15 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67947158</v>
+        <v>67944288</v>
       </c>
       <c r="B15" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>689792.7629640638</v>
+        <v>689907</v>
       </c>
       <c r="R15" t="n">
-        <v>6371631.106853061</v>
+        <v>6371582</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,19 +2041,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,15 +2071,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>67944435</v>
+        <v>67946912</v>
       </c>
       <c r="B16" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,21 +2082,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2327,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>689923.1510330392</v>
+        <v>689899</v>
       </c>
       <c r="R16" t="n">
-        <v>6371614.009107782</v>
+        <v>6371639</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,19 +2141,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,37 +2171,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67944451</v>
+        <v>67947121</v>
       </c>
       <c r="B17" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2442,10 +2208,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>689927.1856759624</v>
+        <v>689876</v>
       </c>
       <c r="R17" t="n">
-        <v>6371620.125227399</v>
+        <v>6371613</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,19 +2241,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,15 +2271,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>67945982</v>
+        <v>67944007</v>
       </c>
       <c r="B18" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,21 +2282,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003295</v>
+        <v>473</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2557,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>689910.2448629305</v>
+        <v>689887</v>
       </c>
       <c r="R18" t="n">
-        <v>6371636.041903548</v>
+        <v>6371500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,19 +2341,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,37 +2371,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>67947218</v>
+        <v>67944445</v>
       </c>
       <c r="B19" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3762</v>
+        <v>473</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2672,10 +2408,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>689661.2322250595</v>
+        <v>689927</v>
       </c>
       <c r="R19" t="n">
-        <v>6371811.979626943</v>
+        <v>6371620</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,19 +2441,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,37 +2471,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67944393</v>
+        <v>67943929</v>
       </c>
       <c r="B20" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>248955</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2787,10 +2508,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>689903.2531392656</v>
+        <v>689918</v>
       </c>
       <c r="R20" t="n">
-        <v>6371623.859964772</v>
+        <v>6371492</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2820,19 +2541,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,37 +2571,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>67946224</v>
+        <v>67943973</v>
       </c>
       <c r="B21" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2902,10 +2608,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>689910.2448629305</v>
+        <v>689904</v>
       </c>
       <c r="R21" t="n">
-        <v>6371636.041903548</v>
+        <v>6371501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,19 +2641,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,32 +2671,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67947121</v>
+        <v>67944029</v>
       </c>
       <c r="B22" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3017,10 +2708,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>689876.2256883241</v>
+        <v>689880</v>
       </c>
       <c r="R22" t="n">
-        <v>6371612.899953701</v>
+        <v>6371495</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3050,19 +2741,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,37 +2771,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67947098</v>
+        <v>67944061</v>
       </c>
       <c r="B23" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3132,10 +2808,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>689858.82127884</v>
+        <v>689869</v>
       </c>
       <c r="R23" t="n">
-        <v>6371604.00523118</v>
+        <v>6371495</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,19 +2841,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,32 +2871,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67944055</v>
+        <v>67944091</v>
       </c>
       <c r="B24" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3247,10 +2908,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>689868.757102189</v>
+        <v>689904</v>
       </c>
       <c r="R24" t="n">
-        <v>6371495.066984033</v>
+        <v>6371549</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3280,19 +2941,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,32 +2971,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>67944288</v>
+        <v>67944303</v>
       </c>
       <c r="B25" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3362,10 +3008,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>689906.8244179436</v>
+        <v>689910</v>
       </c>
       <c r="R25" t="n">
-        <v>6371581.990973721</v>
+        <v>6371578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3395,19 +3041,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,15 +3071,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67943973</v>
+        <v>67944455</v>
       </c>
       <c r="B26" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>689904.1181402666</v>
+        <v>689927</v>
       </c>
       <c r="R26" t="n">
-        <v>6371501.026259615</v>
+        <v>6371620</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3510,19 +3141,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,37 +3171,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>67944104</v>
+        <v>67944822</v>
       </c>
       <c r="B27" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3592,10 +3208,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>689947.0970134967</v>
+        <v>689926</v>
       </c>
       <c r="R27" t="n">
-        <v>6371552.071808753</v>
+        <v>6371638</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3625,19 +3241,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,15 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67947169</v>
+        <v>67946116</v>
       </c>
       <c r="B28" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,21 +3282,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3707,10 +3308,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>689757.9682361817</v>
+        <v>689910</v>
       </c>
       <c r="R28" t="n">
-        <v>6371670.982152543</v>
+        <v>6371636</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3740,19 +3341,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3780,15 +3371,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67946116</v>
+        <v>67946845</v>
       </c>
       <c r="B29" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3822,10 +3408,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>689910.2448629305</v>
+        <v>689899</v>
       </c>
       <c r="R29" t="n">
-        <v>6371636.041903548</v>
+        <v>6371639</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3855,19 +3441,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,15 +3471,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>67947073</v>
+        <v>67947059</v>
       </c>
       <c r="B30" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3937,10 +3508,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>689835.1510304722</v>
+        <v>689862</v>
       </c>
       <c r="R30" t="n">
-        <v>6371544.16024012</v>
+        <v>6371574</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3970,19 +3541,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,37 +3571,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>67944214</v>
+        <v>67947073</v>
       </c>
       <c r="B31" t="n">
-        <v>85138</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>248952</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4052,10 +3608,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>689938.1871756627</v>
+        <v>689835</v>
       </c>
       <c r="R31" t="n">
-        <v>6371615.787819861</v>
+        <v>6371544</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4085,19 +3641,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,19 +3671,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>67944257</v>
+        <v>67944044</v>
       </c>
       <c r="B32" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4167,10 +3708,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>689915.8835991096</v>
+        <v>689875</v>
       </c>
       <c r="R32" t="n">
-        <v>6371607.74230447</v>
+        <v>6371498</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4200,19 +3741,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,37 +3771,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>67947209</v>
+        <v>67944120</v>
       </c>
       <c r="B33" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4282,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>689673.9362462962</v>
+        <v>689939</v>
       </c>
       <c r="R33" t="n">
-        <v>6371794.248892434</v>
+        <v>6371567</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4315,19 +3841,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,15 +3871,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>67944132</v>
+        <v>67944216</v>
       </c>
       <c r="B34" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4371,21 +3882,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +3908,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>689923.1137365925</v>
+        <v>689938</v>
       </c>
       <c r="R34" t="n">
-        <v>6371580.055605051</v>
+        <v>6371616</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4430,19 +3941,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,37 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>67944468</v>
+        <v>67944257</v>
       </c>
       <c r="B35" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4512,10 +4008,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>689938.9512754497</v>
+        <v>689916</v>
       </c>
       <c r="R35" t="n">
-        <v>6371634.146496345</v>
+        <v>6371608</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4545,19 +4041,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4585,15 +4071,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67944328</v>
+        <v>67944310</v>
       </c>
       <c r="B36" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4601,21 +4082,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4627,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>689884.2073656609</v>
+        <v>689910</v>
       </c>
       <c r="R36" t="n">
-        <v>6371592.254199082</v>
+        <v>6371578</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4660,19 +4141,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4700,37 +4171,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>67944303</v>
+        <v>67944386</v>
       </c>
       <c r="B37" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4742,10 +4208,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>689910.2577230593</v>
+        <v>689903</v>
       </c>
       <c r="R37" t="n">
-        <v>6371577.839639137</v>
+        <v>6371624</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4775,19 +4241,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4815,37 +4271,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67947110</v>
+        <v>67944451</v>
       </c>
       <c r="B38" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4857,10 +4308,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>689879.884470762</v>
+        <v>689927</v>
       </c>
       <c r="R38" t="n">
-        <v>6371603.908903114</v>
+        <v>6371620</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4890,19 +4341,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4930,15 +4371,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>67944195</v>
+        <v>67944927</v>
       </c>
       <c r="B39" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4946,21 +4382,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4972,10 +4408,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>689957.1703622936</v>
+        <v>689926</v>
       </c>
       <c r="R39" t="n">
-        <v>6371613.978191566</v>
+        <v>6371638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5005,19 +4441,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5045,19 +4471,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>67945405</v>
+        <v>67947169</v>
       </c>
       <c r="B40" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5087,10 +4508,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>689925.8197188232</v>
+        <v>689758</v>
       </c>
       <c r="R40" t="n">
-        <v>6371637.845677878</v>
+        <v>6371671</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5120,19 +4541,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5160,37 +4571,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>67946776</v>
+        <v>67947197</v>
       </c>
       <c r="B41" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>248956</v>
+        <v>3712</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5202,10 +4608,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>689898.7798446383</v>
+        <v>689681</v>
       </c>
       <c r="R41" t="n">
-        <v>6371638.741019734</v>
+        <v>6371801</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5235,19 +4641,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5275,37 +4671,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>67947149</v>
+        <v>67944013</v>
       </c>
       <c r="B42" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5317,10 +4708,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>689810.2183107834</v>
+        <v>689887</v>
       </c>
       <c r="R42" t="n">
-        <v>6371685.271763251</v>
+        <v>6371500</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5350,19 +4741,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5393,12 +4774,7 @@
         <v>67944753</v>
       </c>
       <c r="B43" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5432,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>689925.8197188232</v>
+        <v>689926</v>
       </c>
       <c r="R43" t="n">
-        <v>6371637.845677878</v>
+        <v>6371638</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5465,19 +4841,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,37 +4871,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>67944461</v>
+        <v>67947130</v>
       </c>
       <c r="B44" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5547,10 +4908,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>689927.1856759624</v>
+        <v>689865</v>
       </c>
       <c r="R44" t="n">
-        <v>6371620.125227399</v>
+        <v>6371648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5580,19 +4941,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5620,37 +4971,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67947086</v>
+        <v>67947218</v>
       </c>
       <c r="B45" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>424</v>
+        <v>3762</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5662,10 +5008,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>689821.7822654031</v>
+        <v>689661</v>
       </c>
       <c r="R45" t="n">
-        <v>6371610.902178471</v>
+        <v>6371812</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5695,19 +5041,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5735,37 +5071,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>67944077</v>
+        <v>67944214</v>
       </c>
       <c r="B46" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87204</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>248952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Brandrud) Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5777,10 +5108,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>689885.0718461988</v>
+        <v>689938</v>
       </c>
       <c r="R46" t="n">
-        <v>6371515.767566406</v>
+        <v>6371616</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5810,19 +5141,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5850,37 +5171,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>67944061</v>
+        <v>67945670</v>
       </c>
       <c r="B47" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87204</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3674</v>
+        <v>248952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brandrud) Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5892,10 +5208,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>689868.757102189</v>
+        <v>689926</v>
       </c>
       <c r="R47" t="n">
-        <v>6371495.066984033</v>
+        <v>6371638</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5925,19 +5241,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5965,15 +5271,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>67944249</v>
+        <v>67943953</v>
       </c>
       <c r="B48" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87291</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5981,21 +5282,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>248956</v>
+        <v>248955</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6007,10 +5308,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>689920.193970543</v>
+        <v>689906</v>
       </c>
       <c r="R48" t="n">
-        <v>6371607.94321084</v>
+        <v>6371473</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6040,19 +5341,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6080,15 +5371,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>67946707</v>
+        <v>67944238</v>
       </c>
       <c r="B49" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87291</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6096,21 +5382,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>424</v>
+        <v>248955</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6122,10 +5408,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>689898.7798446383</v>
+        <v>689926</v>
       </c>
       <c r="R49" t="n">
-        <v>6371638.741019734</v>
+        <v>6371609</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6155,19 +5441,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6195,37 +5471,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>67944216</v>
+        <v>67944354</v>
       </c>
       <c r="B50" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87291</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3712</v>
+        <v>248955</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6237,10 +5508,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>689938.1871756627</v>
+        <v>689901</v>
       </c>
       <c r="R50" t="n">
-        <v>6371615.787819861</v>
+        <v>6371607</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6270,19 +5541,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6310,37 +5571,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>67944085</v>
+        <v>67944393</v>
       </c>
       <c r="B51" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87291</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6003295</v>
+        <v>248955</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6352,10 +5608,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>689904.0428216576</v>
+        <v>689903</v>
       </c>
       <c r="R51" t="n">
-        <v>6371548.987167462</v>
+        <v>6371624</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6385,19 +5641,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6425,37 +5671,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>67944044</v>
+        <v>67944041</v>
       </c>
       <c r="B52" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6467,10 +5708,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>689875.0975444769</v>
+        <v>689875</v>
       </c>
       <c r="R52" t="n">
-        <v>6371498.057075401</v>
+        <v>6371498</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6500,19 +5741,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6540,15 +5771,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>67946912</v>
+        <v>67944249</v>
       </c>
       <c r="B53" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6556,21 +5782,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6582,10 +5808,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>689898.7798446383</v>
+        <v>689920</v>
       </c>
       <c r="R53" t="n">
-        <v>6371638.741019734</v>
+        <v>6371608</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6615,19 +5841,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6655,15 +5871,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>67947185</v>
+        <v>67944366</v>
       </c>
       <c r="B54" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6671,21 +5882,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6697,10 +5908,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>689788.2543717989</v>
+        <v>689904</v>
       </c>
       <c r="R54" t="n">
-        <v>6371727.899587199</v>
+        <v>6371615</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6730,19 +5941,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6770,37 +5971,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>67947059</v>
+        <v>67944426</v>
       </c>
       <c r="B55" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6812,10 +6008,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>689861.8408516926</v>
+        <v>689917</v>
       </c>
       <c r="R55" t="n">
-        <v>6371573.966576695</v>
+        <v>6371625</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6845,19 +6041,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6885,15 +6071,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>67944238</v>
+        <v>67944435</v>
       </c>
       <c r="B56" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6901,21 +6082,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>248955</v>
+        <v>248956</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6927,10 +6108,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>689926.0956656017</v>
+        <v>689923</v>
       </c>
       <c r="R56" t="n">
-        <v>6371608.75721164</v>
+        <v>6371614</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6960,19 +6141,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7000,37 +6171,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>67944822</v>
+        <v>67944468</v>
       </c>
       <c r="B57" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7042,10 +6208,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>689925.8197188232</v>
+        <v>689939</v>
       </c>
       <c r="R57" t="n">
-        <v>6371637.845677878</v>
+        <v>6371634</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7075,19 +6241,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7115,15 +6271,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>67947043</v>
+        <v>67946224</v>
       </c>
       <c r="B58" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7157,10 +6308,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>689899.7696686545</v>
+        <v>689910</v>
       </c>
       <c r="R58" t="n">
-        <v>6371652.259906288</v>
+        <v>6371636</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7190,19 +6341,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7230,15 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>67947180</v>
+        <v>67946776</v>
       </c>
       <c r="B59" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7246,21 +6382,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7272,10 +6408,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>689771.0757089619</v>
+        <v>689899</v>
       </c>
       <c r="R59" t="n">
-        <v>6371714.165876884</v>
+        <v>6371639</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7305,19 +6441,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7345,37 +6471,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>67944029</v>
+        <v>67947043</v>
       </c>
       <c r="B60" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7387,10 +6508,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>689880.0971965204</v>
+        <v>689900</v>
       </c>
       <c r="R60" t="n">
-        <v>6371495.056474297</v>
+        <v>6371652</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7420,19 +6541,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7460,37 +6571,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>67944310</v>
+        <v>67947098</v>
       </c>
       <c r="B61" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7502,10 +6608,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>689910.2577230593</v>
+        <v>689859</v>
       </c>
       <c r="R61" t="n">
-        <v>6371577.839639137</v>
+        <v>6371604</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7535,19 +6641,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7575,15 +6671,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>67945670</v>
+        <v>67947209</v>
       </c>
       <c r="B62" t="n">
-        <v>85138</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7591,21 +6682,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248952</v>
+        <v>248956</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7617,10 +6708,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>689925.8197188232</v>
+        <v>689674</v>
       </c>
       <c r="R62" t="n">
-        <v>6371637.845677878</v>
+        <v>6371794</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7650,19 +6741,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7690,37 +6771,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>67944271</v>
+        <v>67943938</v>
       </c>
       <c r="B63" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7732,10 +6808,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>689911.9868441303</v>
+        <v>689918</v>
       </c>
       <c r="R63" t="n">
-        <v>6371587.081846434</v>
+        <v>6371492</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7765,19 +6841,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7805,37 +6871,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>67947070</v>
+        <v>67943995</v>
       </c>
       <c r="B64" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7847,10 +6908,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>689835.1510304722</v>
+        <v>689894</v>
       </c>
       <c r="R64" t="n">
-        <v>6371544.16024012</v>
+        <v>6371499</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7880,19 +6941,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7920,37 +6971,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>67947225</v>
+        <v>67944077</v>
       </c>
       <c r="B65" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7962,10 +7008,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>689692.215350255</v>
+        <v>689885</v>
       </c>
       <c r="R65" t="n">
-        <v>6371761.149827708</v>
+        <v>6371516</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7995,19 +7041,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8035,37 +7071,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>67944354</v>
+        <v>67944085</v>
       </c>
       <c r="B66" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>248955</v>
+        <v>6003295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8077,10 +7108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>689900.7972981008</v>
+        <v>689904</v>
       </c>
       <c r="R66" t="n">
-        <v>6371607.039168129</v>
+        <v>6371549</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8110,19 +7141,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8150,37 +7171,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>67947197</v>
+        <v>67944104</v>
       </c>
       <c r="B67" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8192,10 +7208,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>689681.1786389069</v>
+        <v>689947</v>
       </c>
       <c r="R67" t="n">
-        <v>6371801.052699062</v>
+        <v>6371552</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8225,19 +7241,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8265,15 +7271,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67944445</v>
+        <v>67944132</v>
       </c>
       <c r="B68" t="n">
-        <v>85222</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8281,21 +7282,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>473</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8307,10 +7308,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>689927.1856759624</v>
+        <v>689923</v>
       </c>
       <c r="R68" t="n">
-        <v>6371620.125227399</v>
+        <v>6371580</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8340,19 +7341,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8380,37 +7371,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>67944013</v>
+        <v>67944195</v>
       </c>
       <c r="B69" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8422,10 +7408,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>689886.8762025242</v>
+        <v>689957</v>
       </c>
       <c r="R69" t="n">
-        <v>6371500.222738158</v>
+        <v>6371614</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8455,19 +7441,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8495,37 +7471,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>67947130</v>
+        <v>67944328</v>
       </c>
       <c r="B70" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8537,10 +7508,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>689864.8735687998</v>
+        <v>689884</v>
       </c>
       <c r="R70" t="n">
-        <v>6371647.939134699</v>
+        <v>6371592</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8570,19 +7541,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8610,37 +7571,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>67947164</v>
+        <v>67944461</v>
       </c>
       <c r="B71" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8652,10 +7608,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>689799.2034316111</v>
+        <v>689927</v>
       </c>
       <c r="R71" t="n">
-        <v>6371631.945763329</v>
+        <v>6371620</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8685,19 +7641,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8725,37 +7671,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>67946845</v>
+        <v>67945982</v>
       </c>
       <c r="B72" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8767,10 +7708,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>689898.7798446383</v>
+        <v>689910</v>
       </c>
       <c r="R72" t="n">
-        <v>6371638.741019734</v>
+        <v>6371636</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8800,19 +7741,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8840,37 +7771,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>67943953</v>
+        <v>67947062</v>
       </c>
       <c r="B73" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>248955</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8882,10 +7808,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>689905.9601957665</v>
+        <v>689862</v>
       </c>
       <c r="R73" t="n">
-        <v>6371473.087694751</v>
+        <v>6371574</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8915,19 +7841,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8955,37 +7871,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>67944386</v>
+        <v>67947149</v>
       </c>
       <c r="B74" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8997,10 +7908,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>689903.2531392656</v>
+        <v>689810</v>
       </c>
       <c r="R74" t="n">
-        <v>6371623.859964772</v>
+        <v>6371685</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9030,19 +7941,9 @@
           <t>2017-10-04</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2017-10-04</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 3324-2023 artfynd.xlsx
+++ b/artfynd/A 3324-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67943914</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944271</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67946707</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947070</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947086</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947110</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,6 +1407,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947164</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947180</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947185</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947225</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1868,6 +1928,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947158</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944055</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2068,6 +2138,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944288</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2168,6 +2243,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67946912</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947121</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2368,6 +2453,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944007</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2468,6 +2558,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944445</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2568,6 +2663,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67943929</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2668,6 +2768,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67943973</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2768,6 +2873,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944029</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2868,6 +2978,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944061</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2968,6 +3083,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944091</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3068,6 +3188,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944303</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3168,6 +3293,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944455</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3268,6 +3398,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944822</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3368,6 +3503,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67946116</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3468,6 +3608,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67946845</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3568,6 +3713,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947059</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3668,6 +3818,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947073</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3768,6 +3923,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944044</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3868,6 +4028,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944120</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3968,6 +4133,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944216</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4068,6 +4238,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944257</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4168,6 +4343,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944310</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4268,6 +4448,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944386</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4368,6 +4553,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944451</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4468,6 +4658,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944927</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4568,6 +4763,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947169</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4668,6 +4868,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947197</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4768,6 +4973,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944013</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4868,6 +5078,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944753</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4968,6 +5183,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947130</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5068,6 +5288,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947218</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5168,6 +5393,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944214</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5268,6 +5498,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67945670</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5368,6 +5603,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67943953</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5468,6 +5708,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944238</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5568,6 +5813,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944354</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5668,6 +5918,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944393</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5768,6 +6023,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944041</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5868,6 +6128,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944249</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5968,6 +6233,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944366</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6068,6 +6338,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944426</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6168,6 +6443,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944435</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6268,6 +6548,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944468</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6368,6 +6653,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67946224</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6468,6 +6758,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67946776</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6568,6 +6863,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947043</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6668,6 +6968,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947098</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6768,6 +7073,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947209</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6868,6 +7178,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67943938</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6968,6 +7283,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67943995</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7068,6 +7388,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944077</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7168,6 +7493,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944085</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7268,6 +7598,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944104</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7368,6 +7703,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944132</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7468,6 +7808,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944195</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7568,6 +7913,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944328</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7668,6 +8018,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67944461</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7768,6 +8123,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67945982</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7868,6 +8228,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947062</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7968,8 +8333,88 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67947149</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>